--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_LUCENTUM ALICANTE.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_LUCENTUM ALICANTE.xlsx
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. STANESCU</t>
+          <t>A. HERNANDEZ TORRO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1905</v>
+        <v>-0.0165</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1941999999999999</v>
+        <v>0.6173999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9962999999999999</v>
+        <v>-0.6339</v>
       </c>
       <c r="G3" t="n">
-        <v>-4.3818</v>
+        <v>0.1722</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.7795000000000001</v>
+        <v>0.0423</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.6024</v>
+        <v>0.1299</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.4713</v>
+        <v>0.6762</v>
       </c>
       <c r="K3" t="n">
-        <v>2.2616</v>
+        <v>0.6762</v>
       </c>
       <c r="L3" t="n">
-        <v>-3.7329</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.9106</v>
+        <v>-0.504</v>
       </c>
       <c r="N3" t="n">
-        <v>-3.0412</v>
+        <v>-0.6339</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1304</v>
+        <v>0.1299</v>
       </c>
       <c r="P3" t="n">
-        <v>2.2644</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.2079</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1005</v>
+        <v>-0.1887</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3637</v>
+        <v>-0.0588</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2632</v>
+        <v>-0.1299</v>
       </c>
       <c r="V3" t="n">
-        <v>2.2076</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.9623999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. HERNANDEZ TORRO</t>
+          <t>F. MARTI GONZALEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. MARTI GONZALEZ</t>
+          <t>R. STANESCU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,70 +796,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0165</v>
+        <v>-0.2925</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6173999999999999</v>
+        <v>-0.9161999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6339</v>
+        <v>0.6237000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1722</v>
+        <v>-4.3818</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0423</v>
+        <v>-0.7795000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1299</v>
+        <v>-3.6024</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6762</v>
+        <v>-1.4713</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6762</v>
+        <v>2.2616</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-3.7329</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.504</v>
+        <v>-2.9106</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6339</v>
+        <v>-3.0412</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1299</v>
+        <v>0.1304</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.2644</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>3.2079</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1887</v>
+        <v>-0.3827</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0588</v>
+        <v>0.2533</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1299</v>
+        <v>-0.6358999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>2.2076</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.9623999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.2466</v>
+        <v>-1.1613</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7037</v>
+        <v>-0.6448999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5428999999999999</v>
+        <v>-0.5164</v>
       </c>
       <c r="G6" t="n">
         <v>-0.9601999999999999</v>
@@ -922,13 +922,13 @@
         <v>0.5661</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2299</v>
+        <v>-0.1446</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1176</v>
+        <v>-0.0588</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1123</v>
+        <v>-0.08579999999999999</v>
       </c>
       <c r="V6" t="n">
         <v>-0.6226</v>
@@ -955,13 +955,13 @@
         <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.786</v>
+        <v>-1.4768</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2314000000000001</v>
+        <v>0.3288</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.0174</v>
+        <v>-1.8055</v>
       </c>
       <c r="G7" t="n">
         <v>-4.270300000000001</v>
@@ -1000,13 +1000,13 @@
         <v>3.0192</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.78</v>
+        <v>-1.4709</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4921</v>
+        <v>-0.3947</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.2881</v>
+        <v>-1.0761</v>
       </c>
       <c r="V7" t="n">
         <v>1.2452</v>
@@ -1033,13 +1033,13 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.0855</v>
+        <v>-3.9088</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2828</v>
+        <v>-0.1854000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.8028</v>
+        <v>-3.7234</v>
       </c>
       <c r="G8" t="n">
         <v>-0.9469000000000001</v>
@@ -1078,13 +1078,13 @@
         <v>0.9435</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2898</v>
+        <v>-1.1129</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2077</v>
+        <v>-0.1102</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.0822</v>
+        <v>-1.0029</v>
       </c>
       <c r="V8" t="n">
         <v>-0.9054</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. TUNEZ CASTILLO</t>
+          <t>T. SODERMAN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>-7.0559</v>
+        <v>-6.731499999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.3769</v>
+        <v>6.7421</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.679</v>
+        <v>-13.4737</v>
       </c>
       <c r="G9" t="n">
-        <v>-5.4221</v>
+        <v>-5.321</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.3636</v>
+        <v>-4.8644</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.0585</v>
+        <v>-0.4564999999999995</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.0936</v>
+        <v>11.0797</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.4852</v>
+        <v>9.351900000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6084000000000001</v>
+        <v>1.7277</v>
       </c>
       <c r="M9" t="n">
-        <v>-4.3284</v>
+        <v>-16.4006</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.8784</v>
+        <v>-14.2164</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.4501</v>
+        <v>-2.1845</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7548</v>
+        <v>2.0757</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1322</v>
+        <v>-10.9446</v>
       </c>
       <c r="R9" t="n">
-        <v>1.887</v>
+        <v>13.0203</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.0869</v>
+        <v>-3.4412</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1511</v>
+        <v>-0.2034000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9358</v>
+        <v>-3.2374</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3018</v>
+        <v>-0.04520000000000024</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>6.810599999999999</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.3018</v>
+        <v>-6.8558</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T. SODERMAN</t>
+          <t>C. TUNEZ CASTILLO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>-9.3531</v>
+        <v>-6.8082</v>
       </c>
       <c r="E10" t="n">
-        <v>5.1428</v>
+        <v>-3.1821</v>
       </c>
       <c r="F10" t="n">
-        <v>-14.496</v>
+        <v>-3.6261</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.321</v>
+        <v>-5.4221</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.8644</v>
+        <v>-3.3636</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4564999999999995</v>
+        <v>-2.0585</v>
       </c>
       <c r="J10" t="n">
-        <v>11.0797</v>
+        <v>-1.0936</v>
       </c>
       <c r="K10" t="n">
-        <v>9.351900000000001</v>
+        <v>-0.4852</v>
       </c>
       <c r="L10" t="n">
-        <v>1.7277</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-16.4006</v>
+        <v>-4.3284</v>
       </c>
       <c r="N10" t="n">
-        <v>-14.2164</v>
+        <v>-2.8784</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.1845</v>
+        <v>-1.4501</v>
       </c>
       <c r="P10" t="n">
-        <v>2.0757</v>
+        <v>0.7548</v>
       </c>
       <c r="Q10" t="n">
-        <v>-10.9446</v>
+        <v>-1.1322</v>
       </c>
       <c r="R10" t="n">
-        <v>13.0203</v>
+        <v>1.887</v>
       </c>
       <c r="S10" t="n">
-        <v>-6.0626</v>
+        <v>-1.8391</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.8029</v>
+        <v>-0.9563</v>
       </c>
       <c r="U10" t="n">
-        <v>-4.2596</v>
+        <v>-0.8829</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.04520000000000024</v>
+        <v>-0.3018</v>
       </c>
       <c r="W10" t="n">
-        <v>6.810599999999999</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-6.8558</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. MASSAMBA JOHANSSON</t>
+          <t>J. CONNELLY IV</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D11" t="n">
-        <v>-12.4768</v>
+        <v>-9.486900000000002</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.6546</v>
+        <v>21.3994</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.8223</v>
+        <v>-30.8861</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.0117</v>
+        <v>0.06740000000000101</v>
       </c>
       <c r="H11" t="n">
-        <v>-5.266100000000001</v>
+        <v>-20.3859</v>
       </c>
       <c r="I11" t="n">
-        <v>1.2544</v>
+        <v>20.4533</v>
       </c>
       <c r="J11" t="n">
-        <v>0.918</v>
+        <v>54.0931</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.7897000000000001</v>
+        <v>16.7165</v>
       </c>
       <c r="L11" t="n">
-        <v>1.7078</v>
+        <v>37.3768</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.9297</v>
+        <v>-54.0256</v>
       </c>
       <c r="N11" t="n">
-        <v>-4.4765</v>
+        <v>-37.1023</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4534</v>
+        <v>-16.9233</v>
       </c>
       <c r="P11" t="n">
-        <v>-5.2836</v>
+        <v>-15.096</v>
       </c>
       <c r="Q11" t="n">
-        <v>-13.7751</v>
+        <v>-55.2891</v>
       </c>
       <c r="R11" t="n">
-        <v>8.4915</v>
+        <v>40.1931</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.6799</v>
+        <v>-12.9356</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.7028</v>
+        <v>-8.2689</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.9772999999999999</v>
+        <v>-4.6669</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5015000000000001</v>
+        <v>18.4776</v>
       </c>
       <c r="W11" t="n">
-        <v>5.9052</v>
+        <v>30.864</v>
       </c>
       <c r="X11" t="n">
-        <v>-6.406700000000001</v>
+        <v>-12.3866</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. CONNELLY IV</t>
+          <t>S. MASSAMBA JOHANSSON</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>-13.5963</v>
+        <v>-11.0853</v>
       </c>
       <c r="E12" t="n">
-        <v>16.4438</v>
+        <v>-7.4651</v>
       </c>
       <c r="F12" t="n">
-        <v>-30.0401</v>
+        <v>-3.62</v>
       </c>
       <c r="G12" t="n">
-        <v>0.06740000000000101</v>
+        <v>-4.0117</v>
       </c>
       <c r="H12" t="n">
-        <v>-20.3859</v>
+        <v>-5.266100000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>20.4533</v>
+        <v>1.2544</v>
       </c>
       <c r="J12" t="n">
-        <v>54.0931</v>
+        <v>0.918</v>
       </c>
       <c r="K12" t="n">
-        <v>16.7165</v>
+        <v>-0.7897000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>37.3768</v>
+        <v>1.7078</v>
       </c>
       <c r="M12" t="n">
-        <v>-54.0256</v>
+        <v>-4.9297</v>
       </c>
       <c r="N12" t="n">
-        <v>-37.1023</v>
+        <v>-4.4765</v>
       </c>
       <c r="O12" t="n">
-        <v>-16.9233</v>
+        <v>-0.4534</v>
       </c>
       <c r="P12" t="n">
-        <v>-15.096</v>
+        <v>-5.2836</v>
       </c>
       <c r="Q12" t="n">
-        <v>-55.2891</v>
+        <v>-13.7751</v>
       </c>
       <c r="R12" t="n">
-        <v>40.1931</v>
+        <v>8.4915</v>
       </c>
       <c r="S12" t="n">
-        <v>-17.0453</v>
+        <v>-1.2886</v>
       </c>
       <c r="T12" t="n">
-        <v>-13.2244</v>
+        <v>-0.5134</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.8209</v>
+        <v>-0.7751</v>
       </c>
       <c r="V12" t="n">
-        <v>18.4776</v>
+        <v>-0.5015000000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>30.864</v>
+        <v>5.9052</v>
       </c>
       <c r="X12" t="n">
-        <v>-12.3866</v>
+        <v>-6.406700000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>-15.2849</v>
+        <v>-13.9284</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.127999999999999</v>
+        <v>-5.192200000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-9.156799999999999</v>
+        <v>-8.735899999999999</v>
       </c>
       <c r="G13" t="n">
         <v>-7.3708</v>
@@ -1468,13 +1468,13 @@
         <v>5.472300000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.273000000000001</v>
+        <v>-2.9165</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.2283</v>
+        <v>-1.2925</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.0451</v>
+        <v>-1.624</v>
       </c>
       <c r="V13" t="n">
         <v>-4.0184</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. BLEDA MIRANDA</t>
+          <t>J. SANABRIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>-16.3469</v>
+        <v>-17.8817</v>
       </c>
       <c r="E14" t="n">
-        <v>13.6522</v>
+        <v>-6.317400000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-29.9993</v>
+        <v>-11.5643</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.2264</v>
+        <v>-8.004200000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.896999999999999</v>
+        <v>-5.926600000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3292</v>
+        <v>-2.0775</v>
       </c>
       <c r="J14" t="n">
-        <v>26.1079</v>
+        <v>2.5593</v>
       </c>
       <c r="K14" t="n">
-        <v>16.3104</v>
+        <v>1.3906</v>
       </c>
       <c r="L14" t="n">
-        <v>9.797599999999999</v>
+        <v>1.1687</v>
       </c>
       <c r="M14" t="n">
-        <v>-28.3343</v>
+        <v>-10.5635</v>
       </c>
       <c r="N14" t="n">
-        <v>-18.2075</v>
+        <v>-7.3173</v>
       </c>
       <c r="O14" t="n">
-        <v>-10.127</v>
+        <v>-3.2462</v>
       </c>
       <c r="P14" t="n">
-        <v>-5.0949</v>
+        <v>-4.528799999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-27.7389</v>
+        <v>-7.548</v>
       </c>
       <c r="R14" t="n">
-        <v>22.644</v>
+        <v>3.0192</v>
       </c>
       <c r="S14" t="n">
-        <v>9.641300000000001</v>
+        <v>-2.8584</v>
       </c>
       <c r="T14" t="n">
-        <v>12.0776</v>
+        <v>-1.2909</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.4363</v>
+        <v>-1.5676</v>
       </c>
       <c r="V14" t="n">
-        <v>-18.6665</v>
+        <v>-2.4904</v>
       </c>
       <c r="W14" t="n">
-        <v>3.2059</v>
+        <v>-0.03799999999999981</v>
       </c>
       <c r="X14" t="n">
-        <v>-21.8725</v>
+        <v>-2.4524</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. SANABRIA</t>
+          <t>C. BLEDA MIRANDA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="D15" t="n">
-        <v>-19.2218</v>
+        <v>-28.4795</v>
       </c>
       <c r="E15" t="n">
-        <v>-7.2918</v>
+        <v>3.2891</v>
       </c>
       <c r="F15" t="n">
-        <v>-11.93</v>
+        <v>-31.7686</v>
       </c>
       <c r="G15" t="n">
-        <v>-8.004200000000001</v>
+        <v>-2.2264</v>
       </c>
       <c r="H15" t="n">
-        <v>-5.926600000000001</v>
+        <v>-1.896999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.0775</v>
+        <v>-0.3292</v>
       </c>
       <c r="J15" t="n">
-        <v>2.5593</v>
+        <v>26.1079</v>
       </c>
       <c r="K15" t="n">
-        <v>1.3906</v>
+        <v>16.3104</v>
       </c>
       <c r="L15" t="n">
-        <v>1.1687</v>
+        <v>9.797599999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-10.5635</v>
+        <v>-28.3343</v>
       </c>
       <c r="N15" t="n">
-        <v>-7.3173</v>
+        <v>-18.2075</v>
       </c>
       <c r="O15" t="n">
-        <v>-3.2462</v>
+        <v>-10.127</v>
       </c>
       <c r="P15" t="n">
-        <v>-4.528799999999999</v>
+        <v>-5.0949</v>
       </c>
       <c r="Q15" t="n">
-        <v>-7.548</v>
+        <v>-27.7389</v>
       </c>
       <c r="R15" t="n">
-        <v>3.0192</v>
+        <v>22.644</v>
       </c>
       <c r="S15" t="n">
-        <v>-4.198399999999999</v>
+        <v>-2.4917</v>
       </c>
       <c r="T15" t="n">
-        <v>-2.2651</v>
+        <v>1.7138</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.9334</v>
+        <v>-4.2055</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.4904</v>
+        <v>-18.6665</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.03799999999999981</v>
+        <v>3.2059</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.4524</v>
+        <v>-21.8725</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. TUDELA GARCIA</t>
+          <t>S. VAL GUTIERREZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,70 +1654,70 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D16" t="n">
-        <v>-25.3355</v>
+        <v>-29.6002</v>
       </c>
       <c r="E16" t="n">
-        <v>10.1831</v>
+        <v>-8.847</v>
       </c>
       <c r="F16" t="n">
-        <v>-35.5183</v>
+        <v>-20.7531</v>
       </c>
       <c r="G16" t="n">
-        <v>-17.5827</v>
+        <v>-5.366999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>-29.9491</v>
+        <v>-17.9131</v>
       </c>
       <c r="I16" t="n">
-        <v>12.3664</v>
+        <v>12.5459</v>
       </c>
       <c r="J16" t="n">
-        <v>32.3711</v>
+        <v>32.1979</v>
       </c>
       <c r="K16" t="n">
-        <v>13.8853</v>
+        <v>11.7782</v>
       </c>
       <c r="L16" t="n">
-        <v>18.486</v>
+        <v>20.4195</v>
       </c>
       <c r="M16" t="n">
-        <v>-49.9537</v>
+        <v>-37.5647</v>
       </c>
       <c r="N16" t="n">
-        <v>-43.8342</v>
+        <v>-29.6911</v>
       </c>
       <c r="O16" t="n">
-        <v>-6.1195</v>
+        <v>-7.8734</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3209</v>
+        <v>-28.305</v>
       </c>
       <c r="Q16" t="n">
-        <v>-39.0609</v>
+        <v>-63.5919</v>
       </c>
       <c r="R16" t="n">
-        <v>40.3818</v>
+        <v>35.2869</v>
       </c>
       <c r="S16" t="n">
-        <v>7.7283</v>
+        <v>-12.0015</v>
       </c>
       <c r="T16" t="n">
-        <v>8.930900000000001</v>
+        <v>-7.393000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.2026</v>
+        <v>-4.6088</v>
       </c>
       <c r="V16" t="n">
-        <v>-16.8017</v>
+        <v>16.0732</v>
       </c>
       <c r="W16" t="n">
-        <v>7.941800000000001</v>
+        <v>29.9396</v>
       </c>
       <c r="X16" t="n">
-        <v>-24.7436</v>
+        <v>-13.8665</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>19</v>
       </c>
       <c r="D17" t="n">
-        <v>-35.0442</v>
+        <v>-34.1574</v>
       </c>
       <c r="E17" t="n">
-        <v>-12.2477</v>
+        <v>-12.5971</v>
       </c>
       <c r="F17" t="n">
-        <v>-22.7964</v>
+        <v>-21.5601</v>
       </c>
       <c r="G17" t="n">
         <v>-16.9062</v>
@@ -1780,13 +1780,13 @@
         <v>12.0768</v>
       </c>
       <c r="S17" t="n">
-        <v>-5.6293</v>
+        <v>-4.7425</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4120999999999997</v>
+        <v>0.06290000000000018</v>
       </c>
       <c r="U17" t="n">
-        <v>-6.041399999999999</v>
+        <v>-4.8054</v>
       </c>
       <c r="V17" t="n">
         <v>-9.4893</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. VAL GUTIERREZ</t>
+          <t>J. MUNOZ PALENCIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,70 +1810,70 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D18" t="n">
-        <v>-35.9481</v>
+        <v>-35.13180000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>-14.9132</v>
+        <v>-12.0812</v>
       </c>
       <c r="F18" t="n">
-        <v>-21.0353</v>
+        <v>-23.0507</v>
       </c>
       <c r="G18" t="n">
-        <v>-5.366999999999999</v>
+        <v>-15.1381</v>
       </c>
       <c r="H18" t="n">
-        <v>-17.9131</v>
+        <v>-19.1375</v>
       </c>
       <c r="I18" t="n">
-        <v>12.5459</v>
+        <v>3.999099999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>32.1979</v>
+        <v>16.2673</v>
       </c>
       <c r="K18" t="n">
-        <v>11.7782</v>
+        <v>8.5724</v>
       </c>
       <c r="L18" t="n">
-        <v>20.4195</v>
+        <v>7.695200000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>-37.5647</v>
+        <v>-31.4053</v>
       </c>
       <c r="N18" t="n">
-        <v>-29.6911</v>
+        <v>-27.7099</v>
       </c>
       <c r="O18" t="n">
-        <v>-7.8734</v>
+        <v>-3.6959</v>
       </c>
       <c r="P18" t="n">
-        <v>-28.305</v>
+        <v>2.0757</v>
       </c>
       <c r="Q18" t="n">
-        <v>-63.5919</v>
+        <v>-31.1355</v>
       </c>
       <c r="R18" t="n">
-        <v>35.2869</v>
+        <v>33.2112</v>
       </c>
       <c r="S18" t="n">
-        <v>-18.3494</v>
+        <v>-16.8853</v>
       </c>
       <c r="T18" t="n">
-        <v>-13.4587</v>
+        <v>-10.5326</v>
       </c>
       <c r="U18" t="n">
-        <v>-4.890700000000001</v>
+        <v>-6.3529</v>
       </c>
       <c r="V18" t="n">
-        <v>16.0732</v>
+        <v>-5.1839</v>
       </c>
       <c r="W18" t="n">
-        <v>29.9396</v>
+        <v>13.3194</v>
       </c>
       <c r="X18" t="n">
-        <v>-13.8665</v>
+        <v>-18.5033</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>12</v>
       </c>
       <c r="D19" t="n">
-        <v>-43.4853</v>
+        <v>-38.7859</v>
       </c>
       <c r="E19" t="n">
-        <v>-17.6587</v>
+        <v>-16.0597</v>
       </c>
       <c r="F19" t="n">
-        <v>-25.8266</v>
+        <v>-22.7263</v>
       </c>
       <c r="G19" t="n">
         <v>-18.8146</v>
@@ -1936,13 +1936,13 @@
         <v>14.5299</v>
       </c>
       <c r="S19" t="n">
-        <v>-11.1398</v>
+        <v>-6.4401</v>
       </c>
       <c r="T19" t="n">
-        <v>-4.033300000000001</v>
+        <v>-2.4338</v>
       </c>
       <c r="U19" t="n">
-        <v>-7.1066</v>
+        <v>-4.0061</v>
       </c>
       <c r="V19" t="n">
         <v>-13.3422</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. MUNOZ PALENCIA</t>
+          <t>G. TUDELA GARCIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,70 +1966,70 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D20" t="n">
-        <v>-44.8599</v>
+        <v>-38.9959</v>
       </c>
       <c r="E20" t="n">
-        <v>-19.3751</v>
+        <v>-1.4046</v>
       </c>
       <c r="F20" t="n">
-        <v>-25.4852</v>
+        <v>-37.5909</v>
       </c>
       <c r="G20" t="n">
-        <v>-15.1381</v>
+        <v>-17.5827</v>
       </c>
       <c r="H20" t="n">
-        <v>-19.1375</v>
+        <v>-29.9491</v>
       </c>
       <c r="I20" t="n">
-        <v>3.999099999999999</v>
+        <v>12.3664</v>
       </c>
       <c r="J20" t="n">
-        <v>16.2673</v>
+        <v>32.3711</v>
       </c>
       <c r="K20" t="n">
-        <v>8.5724</v>
+        <v>13.8853</v>
       </c>
       <c r="L20" t="n">
-        <v>7.695200000000001</v>
+        <v>18.486</v>
       </c>
       <c r="M20" t="n">
-        <v>-31.4053</v>
+        <v>-49.9537</v>
       </c>
       <c r="N20" t="n">
-        <v>-27.7099</v>
+        <v>-43.8342</v>
       </c>
       <c r="O20" t="n">
-        <v>-3.6959</v>
+        <v>-6.1195</v>
       </c>
       <c r="P20" t="n">
-        <v>2.0757</v>
+        <v>1.3209</v>
       </c>
       <c r="Q20" t="n">
-        <v>-31.1355</v>
+        <v>-39.0609</v>
       </c>
       <c r="R20" t="n">
-        <v>33.2112</v>
+        <v>40.3818</v>
       </c>
       <c r="S20" t="n">
-        <v>-26.6135</v>
+        <v>-5.9321</v>
       </c>
       <c r="T20" t="n">
-        <v>-17.8264</v>
+        <v>-2.657</v>
       </c>
       <c r="U20" t="n">
-        <v>-8.786999999999999</v>
+        <v>-3.2752</v>
       </c>
       <c r="V20" t="n">
-        <v>-5.1839</v>
+        <v>-16.8017</v>
       </c>
       <c r="W20" t="n">
-        <v>13.3194</v>
+        <v>7.941800000000001</v>
       </c>
       <c r="X20" t="n">
-        <v>-18.5033</v>
+        <v>-24.7436</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>20</v>
       </c>
       <c r="D21" t="n">
-        <v>-51.6148</v>
+        <v>-50.8821</v>
       </c>
       <c r="E21" t="n">
-        <v>-16.3871</v>
+        <v>-18.351</v>
       </c>
       <c r="F21" t="n">
-        <v>-35.2278</v>
+        <v>-32.5313</v>
       </c>
       <c r="G21" t="n">
         <v>-18.3039</v>
@@ -2092,13 +2092,13 @@
         <v>34.9095</v>
       </c>
       <c r="S21" t="n">
-        <v>-8.894</v>
+        <v>-8.161899999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0548</v>
+        <v>-3.0185</v>
       </c>
       <c r="U21" t="n">
-        <v>-7.8398</v>
+        <v>-5.1433</v>
       </c>
       <c r="V21" t="n">
         <v>-22.3406</v>
@@ -2125,13 +2125,13 @@
         <v>21</v>
       </c>
       <c r="D22" t="n">
-        <v>-75.4015</v>
+        <v>-65.26739999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>-41.208</v>
+        <v>-34.6147</v>
       </c>
       <c r="F22" t="n">
-        <v>-34.1932</v>
+        <v>-30.653</v>
       </c>
       <c r="G22" t="n">
         <v>-55.7516</v>
@@ -2170,13 +2170,13 @@
         <v>36.4191</v>
       </c>
       <c r="S22" t="n">
-        <v>-25.1937</v>
+        <v>-15.0596</v>
       </c>
       <c r="T22" t="n">
-        <v>-14.7739</v>
+        <v>-8.1805</v>
       </c>
       <c r="U22" t="n">
-        <v>-10.4198</v>
+        <v>-6.8791</v>
       </c>
       <c r="V22" t="n">
         <v>-12.194</v>
@@ -2203,13 +2203,13 @@
         <v>23</v>
       </c>
       <c r="D23" t="n">
-        <v>-80.44880000000001</v>
+        <v>-71.3386</v>
       </c>
       <c r="E23" t="n">
-        <v>-31.6059</v>
+        <v>-28.7737</v>
       </c>
       <c r="F23" t="n">
-        <v>-48.8428</v>
+        <v>-42.565</v>
       </c>
       <c r="G23" t="n">
         <v>-46.159</v>
@@ -2248,13 +2248,13 @@
         <v>53.9682</v>
       </c>
       <c r="S23" t="n">
-        <v>-30.8065</v>
+        <v>-21.6968</v>
       </c>
       <c r="T23" t="n">
-        <v>-13.0757</v>
+        <v>-10.2434</v>
       </c>
       <c r="U23" t="n">
-        <v>-17.7313</v>
+        <v>-11.4532</v>
       </c>
       <c r="V23" t="n">
         <v>-18.013</v>
@@ -2281,13 +2281,13 @@
         <v>24</v>
       </c>
       <c r="D24" t="n">
-        <v>-476.7578</v>
+        <v>-450.7565999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-118.0746</v>
+        <v>-108.9615</v>
       </c>
       <c r="F24" t="n">
-        <v>-358.6837</v>
+        <v>-341.7945</v>
       </c>
       <c r="G24" t="n">
         <v>-221.8501</v>
@@ -2296,7 +2296,7 @@
         <v>-225.2919</v>
       </c>
       <c r="I24" t="n">
-        <v>3.442499999999999</v>
+        <v>3.442499999999992</v>
       </c>
       <c r="J24" t="n">
         <v>212.1838</v>
@@ -2323,16 +2323,16 @@
         <v>-383.061</v>
       </c>
       <c r="R24" t="n">
-        <v>363.2475000000001</v>
+        <v>363.2474999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>-148.1793</v>
+        <v>-122.1794</v>
       </c>
       <c r="T24" t="n">
-        <v>-64.74809999999999</v>
+        <v>-55.63550000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-83.4332</v>
+        <v>-66.54389999999999</v>
       </c>
       <c r="V24" t="n">
         <v>-86.91290000000001</v>
